--- a/payroll/2026/excel/20260930-20261001工资.xlsx
+++ b/payroll/2026/excel/20260930-20261001工资.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chrome_dowload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lubaoqiang\git\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C46FA9D-2C4A-4BC0-BE36-E5A5CE7A7A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53DE138-D31C-490C-8239-FDC97A0A8E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="380" windowWidth="22600" windowHeight="13960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="440" windowWidth="22600" windowHeight="13960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工资" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
     <t>一霸归来了</t>
   </si>
   <si>
-    <t>0930-1001 集体产出 2202   行会账户A   往期结存 ( 3822 + 267 = 4,089 )</t>
+    <t>0930-1001 集体产出 2202   行会账户A   往期结存 ( 3822 + 267 = 4,089, 4089 - (350*3=1050 (抚胖桃)) = 3039 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -274,7 +274,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -297,6 +297,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color indexed="8"/>
       <name val="等线"/>
       <family val="3"/>
@@ -359,13 +368,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,15 +698,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -826,38 +835,38 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:9" ht="17.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
